--- a/game-demo/cards_config.xlsx
+++ b/game-demo/cards_config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cards" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Field Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2224,17 +2224,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>warrior_angry_anvil</t>
+          <t>toxin</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>怒砧</t>
+          <t>浊气</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>warrior</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>UNCOMMON</t>
+          <t>COMMON</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2256,13 +2256,13 @@
         <v>1</v>
       </c>
       <c r="H22" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2284,676 +2284,20 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>获得 {block} 点护体，随机消耗 1 张手牌。</t>
+          <t>拖慢你的行动。</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>WarriorCard</t>
+          <t>CultivationCard</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>tile_0074.png</t>
+          <t>tile_0114.png</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>block.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>warrior_axe_attack</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>斧劈</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>ATTACK</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>COMMON</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>SINGLE_ENEMY</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>造成 {damage} 点伤害。</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>tile_0119.png</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>axe.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>warrior_big_slam</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>重击</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>ATTACK</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>UNCOMMON</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>SINGLE_ENEMY</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>造成 {damage} 点伤害，并施加 {exposed} 回合破绽。</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>tile_0117.png</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>slash.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>warrior_block</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>格挡</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>SKILL</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>COMMON</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>获得 {block} 点护体。</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>tile_0102.png</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>block.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>warrior_sharp_knife</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>磨刃</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>ATTACK</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>RARE</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>SINGLE_ENEMY</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>造成 {damage} 点伤害。本场战斗此牌伤害 +{extra}。</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>tile_0105.png</t>
-        </is>
-      </c>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>slash.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>warrior_slash</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>横扫</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>ATTACK</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>COMMON</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>ALL_ENEMIES</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>对所有敌人造成 {damage} 点伤害。</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>tile_0118.png</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>slash.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>warrior_trickster</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>佯攻</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>SKILL</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>UNCOMMON</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>获得 {block} 点护体，抽 1 张牌。</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>tile_0101.png</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>enemy_block.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>warrior_true_strength</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>真武形</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>warrior</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>POWER</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>RARE</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>回合开始时，获得 2 层劲气。</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>WarriorCard</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>tile_0127.png</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>true_strength.ogg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>toxin</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>浊气</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>SKILL</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>COMMON</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>拖慢你的行动。</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>Card</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>tile_0114.png</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="inlineStr">
         <is>
           <t>true_strength.ogg</t>
         </is>
@@ -2961,17 +2305,17 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="D2:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Card Type" error="Please select a valid card type" type="list">
+    <dataValidation sqref="D2:D22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Card Type" error="Please select a valid card type" type="list">
       <formula1>"ATTACK,SKILL,POWER"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Rarity" error="Please select a valid rarity" type="list">
+    <dataValidation sqref="E2:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Rarity" error="Please select a valid rarity" type="list">
       <formula1>"COMMON,UNCOMMON,RARE"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Target" error="Please select a valid target" type="list">
+    <dataValidation sqref="F2:F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Target" error="Please select a valid target" type="list">
       <formula1>"SELF,SINGLE_ENEMY,ALL_ENEMIES,EVERYONE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Character" error="Please select a valid character" type="list">
-      <formula1>"beastmaster,body_cultivator,demonic_cultivator,sword_cultivator,warrior,common"</formula1>
+    <dataValidation sqref="C2:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Character" error="Please select a valid character" type="list">
+      <formula1>"beastmaster,body_cultivator,demonic_cultivator,sword_cultivator,common"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3268,12 +2612,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Extra damage (磨刃 only)</t>
+          <t>Extra damage</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Only for warrior_sharp_knife</t>
+          <t>Reserved for specialized effects</t>
         </is>
       </c>
     </row>
@@ -3307,7 +2651,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>CultivationCard / WarriorCard / Card</t>
+          <t>CultivationCard / Card</t>
         </is>
       </c>
     </row>
